--- a/artfynd/A 43595-2023 artfynd.xlsx
+++ b/artfynd/A 43595-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 43595-2023 artfynd.xlsx
+++ b/artfynd/A 43595-2023 artfynd.xlsx
@@ -4773,10 +4773,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119537049</v>
+        <v>119536821</v>
       </c>
       <c r="B36" t="n">
-        <v>90043</v>
+        <v>91825</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4789,21 +4789,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3286</v>
+        <v>1968</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Bankera violascens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4813,10 +4813,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>540419</v>
+        <v>540329</v>
       </c>
       <c r="R36" t="n">
-        <v>7201871</v>
+        <v>7201760</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4848,7 +4848,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4858,7 +4858,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4885,10 +4885,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119536821</v>
+        <v>119537049</v>
       </c>
       <c r="B37" t="n">
-        <v>91825</v>
+        <v>90043</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4901,21 +4901,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1968</v>
+        <v>3286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4925,10 +4925,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>540329</v>
+        <v>540419</v>
       </c>
       <c r="R37" t="n">
-        <v>7201760</v>
+        <v>7201871</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 43595-2023 artfynd.xlsx
+++ b/artfynd/A 43595-2023 artfynd.xlsx
@@ -4773,10 +4773,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119536821</v>
+        <v>119536251</v>
       </c>
       <c r="B36" t="n">
-        <v>91825</v>
+        <v>91494</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4785,25 +4785,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1968</v>
+        <v>4769</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4813,10 +4813,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>540329</v>
+        <v>540361</v>
       </c>
       <c r="R36" t="n">
-        <v>7201760</v>
+        <v>7201818</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4848,7 +4848,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4858,7 +4858,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4885,10 +4885,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119537049</v>
+        <v>119536761</v>
       </c>
       <c r="B37" t="n">
-        <v>90043</v>
+        <v>87401</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4897,25 +4897,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3286</v>
+        <v>823</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Hyacintvaxskivling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Hygrophorus hyacinthinus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4925,7 +4925,7 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>540419</v>
+        <v>540400</v>
       </c>
       <c r="R37" t="n">
         <v>7201871</v>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4997,7 +4997,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119537047</v>
+        <v>119537049</v>
       </c>
       <c r="B38" t="n">
         <v>90043</v>
@@ -5037,10 +5037,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>540378</v>
+        <v>540419</v>
       </c>
       <c r="R38" t="n">
-        <v>7201863</v>
+        <v>7201871</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -5072,7 +5072,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5091,7 +5091,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5110,10 +5109,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119536402</v>
+        <v>119537047</v>
       </c>
       <c r="B39" t="n">
-        <v>99161</v>
+        <v>90043</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5122,25 +5121,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2082</v>
+        <v>3286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skogsrör</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Calamagrostis chalybaea</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Laest.) Fr.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5150,10 +5149,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>540390</v>
+        <v>540378</v>
       </c>
       <c r="R39" t="n">
-        <v>7201851</v>
+        <v>7201863</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5185,7 +5184,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5195,7 +5194,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5204,6 +5203,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5222,10 +5222,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119536761</v>
+        <v>119536402</v>
       </c>
       <c r="B40" t="n">
-        <v>87401</v>
+        <v>99161</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5234,25 +5234,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>823</v>
+        <v>2082</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hyacintvaxskivling</t>
+          <t>Skogsrör</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hygrophorus hyacinthinus</t>
+          <t>Calamagrostis chalybaea</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Laest.) Fr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5262,10 +5262,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>540400</v>
+        <v>540390</v>
       </c>
       <c r="R40" t="n">
-        <v>7201871</v>
+        <v>7201851</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5297,7 +5297,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5334,10 +5334,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119537050</v>
+        <v>119536821</v>
       </c>
       <c r="B41" t="n">
-        <v>90043</v>
+        <v>91825</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5350,21 +5350,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3286</v>
+        <v>1968</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Bankera violascens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5374,10 +5374,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>540401</v>
+        <v>540329</v>
       </c>
       <c r="R41" t="n">
-        <v>7201866</v>
+        <v>7201760</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5419,7 +5419,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5446,10 +5446,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119536251</v>
+        <v>119537050</v>
       </c>
       <c r="B42" t="n">
-        <v>91494</v>
+        <v>90043</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5458,25 +5458,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4769</v>
+        <v>3286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5486,10 +5486,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>540361</v>
+        <v>540401</v>
       </c>
       <c r="R42" t="n">
-        <v>7201818</v>
+        <v>7201866</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5521,7 +5521,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 43595-2023 artfynd.xlsx
+++ b/artfynd/A 43595-2023 artfynd.xlsx
@@ -4773,10 +4773,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119536251</v>
+        <v>119536402</v>
       </c>
       <c r="B36" t="n">
-        <v>91494</v>
+        <v>99161</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4789,21 +4789,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4769</v>
+        <v>2082</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skogsrör</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Calamagrostis chalybaea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Laest.) Fr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4813,10 +4813,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>540361</v>
+        <v>540390</v>
       </c>
       <c r="R36" t="n">
-        <v>7201818</v>
+        <v>7201851</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4848,7 +4848,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4858,7 +4858,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4885,10 +4885,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119536761</v>
+        <v>119537050</v>
       </c>
       <c r="B37" t="n">
-        <v>87401</v>
+        <v>90043</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4897,25 +4897,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>823</v>
+        <v>3286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hyacintvaxskivling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hygrophorus hyacinthinus</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4925,10 +4925,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>540400</v>
+        <v>540401</v>
       </c>
       <c r="R37" t="n">
-        <v>7201871</v>
+        <v>7201866</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4997,7 +4997,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119537049</v>
+        <v>119537047</v>
       </c>
       <c r="B38" t="n">
         <v>90043</v>
@@ -5037,10 +5037,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>540419</v>
+        <v>540378</v>
       </c>
       <c r="R38" t="n">
-        <v>7201871</v>
+        <v>7201863</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -5072,7 +5072,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5091,6 +5091,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5109,10 +5110,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119537047</v>
+        <v>119536761</v>
       </c>
       <c r="B39" t="n">
-        <v>90043</v>
+        <v>87401</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5121,25 +5122,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3286</v>
+        <v>823</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Hyacintvaxskivling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Hygrophorus hyacinthinus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5149,10 +5150,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>540378</v>
+        <v>540400</v>
       </c>
       <c r="R39" t="n">
-        <v>7201863</v>
+        <v>7201871</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5184,7 +5185,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5194,7 +5195,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5203,7 +5204,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5222,10 +5222,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119536402</v>
+        <v>119536251</v>
       </c>
       <c r="B40" t="n">
-        <v>99161</v>
+        <v>91494</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5238,21 +5238,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2082</v>
+        <v>4769</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skogsrör</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Calamagrostis chalybaea</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Laest.) Fr.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5262,10 +5262,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>540390</v>
+        <v>540361</v>
       </c>
       <c r="R40" t="n">
-        <v>7201851</v>
+        <v>7201818</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5297,7 +5297,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5446,7 +5446,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119537050</v>
+        <v>119537049</v>
       </c>
       <c r="B42" t="n">
         <v>90043</v>
@@ -5486,10 +5486,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>540401</v>
+        <v>540419</v>
       </c>
       <c r="R42" t="n">
-        <v>7201866</v>
+        <v>7201871</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5521,7 +5521,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 43595-2023 artfynd.xlsx
+++ b/artfynd/A 43595-2023 artfynd.xlsx
@@ -5558,7 +5558,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124495747</v>
+        <v>124495808</v>
       </c>
       <c r="B43" t="n">
         <v>83424</v>
@@ -5591,23 +5591,14 @@
           <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Staaloennjuana, Staaloennjuana, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540334</v>
+        <v>540320</v>
       </c>
       <c r="R43" t="n">
         <v>7201784</v>
@@ -5679,10 +5670,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124495808</v>
+        <v>124496447</v>
       </c>
       <c r="B44" t="n">
-        <v>83424</v>
+        <v>100188</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5691,38 +5682,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1445</v>
+        <v>222771</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Staaloennjuana, Staaloennjuana, Ås lm</t>
+          <t>Stalonnäset, Stalonnäset, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540320</v>
+        <v>540359</v>
       </c>
       <c r="R44" t="n">
-        <v>7201784</v>
+        <v>7201824</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5754,7 +5745,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5764,7 +5755,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5791,10 +5782,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124496447</v>
+        <v>124495747</v>
       </c>
       <c r="B45" t="n">
-        <v>100188</v>
+        <v>83424</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5803,38 +5794,47 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222771</v>
+        <v>1445</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Stalonnäset, Stalonnäset, Ås lm</t>
+          <t>Staaloennjuana, Staaloennjuana, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>540359</v>
+        <v>540334</v>
       </c>
       <c r="R45" t="n">
-        <v>7201824</v>
+        <v>7201784</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5866,7 +5866,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6146,7 +6146,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Sara Forsström</t>
+          <t>Sara Forsström, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">

--- a/artfynd/A 43595-2023 artfynd.xlsx
+++ b/artfynd/A 43595-2023 artfynd.xlsx
@@ -5670,10 +5670,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124496447</v>
+        <v>124495747</v>
       </c>
       <c r="B44" t="n">
-        <v>100188</v>
+        <v>83424</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5682,38 +5682,47 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222771</v>
+        <v>1445</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Stalonnäset, Stalonnäset, Ås lm</t>
+          <t>Staaloennjuana, Staaloennjuana, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540359</v>
+        <v>540334</v>
       </c>
       <c r="R44" t="n">
-        <v>7201824</v>
+        <v>7201784</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5745,7 +5754,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5755,7 +5764,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5782,10 +5791,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124495747</v>
+        <v>124496447</v>
       </c>
       <c r="B45" t="n">
-        <v>83424</v>
+        <v>100188</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5794,47 +5803,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1445</v>
+        <v>222771</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Staaloennjuana, Staaloennjuana, Ås lm</t>
+          <t>Stalonnäset, Stalonnäset, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>540334</v>
+        <v>540359</v>
       </c>
       <c r="R45" t="n">
-        <v>7201784</v>
+        <v>7201824</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5866,7 +5866,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5903,7 +5903,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124529574</v>
+        <v>124530286</v>
       </c>
       <c r="B46" t="n">
         <v>83424</v>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5946,6 +5946,8 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Stalons kalkgranskog, Ås lm</t>
@@ -5955,10 +5957,10 @@
         <v>540322</v>
       </c>
       <c r="R46" t="n">
-        <v>7201758</v>
+        <v>7201771</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5985,19 +5987,14 @@
           <t>2025-04-27</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>13:46</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-04-27</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>13:46</t>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ny lokal! Totalt hittades 4 fruktkroppar fördelade under tre olika granar. Statusen på växtplatsen bedöms som god men vinterns stormar har gjort att många kvistar blåst ner från granarna, vilket möjligen påverkar lokalen tillfälligt närmsta åren. Några träd har också blåst omkull i skogen men ingen större påverkan där bombmurklorna växer. Lokalen är oskyddad.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6006,8 +6003,19 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>Kalkrik väldränerad granskog intill Kultsjöån.</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -6020,11 +6028,15 @@
           <t>Isak Vahlström, Sara Forsström</t>
         </is>
       </c>
-      <c r="AY46" t="inlineStr"/>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Uppföljning bombmurkla 2025</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124530286</v>
+        <v>124529574</v>
       </c>
       <c r="B47" t="n">
         <v>83424</v>
@@ -6059,7 +6071,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6067,8 +6079,6 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Stalons kalkgranskog, Ås lm</t>
@@ -6078,10 +6088,10 @@
         <v>540322</v>
       </c>
       <c r="R47" t="n">
-        <v>7201771</v>
+        <v>7201758</v>
       </c>
       <c r="S47" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6108,14 +6118,19 @@
           <t>2025-04-27</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-04-27</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ny lokal! Totalt hittades 4 fruktkroppar fördelade under tre olika granar. Statusen på växtplatsen bedöms som god men vinterns stormar har gjort att många kvistar blåst ner från granarna, vilket möjligen påverkar lokalen tillfälligt närmsta åren. Några träd har också blåst omkull i skogen men ingen större påverkan där bombmurklorna växer. Lokalen är oskyddad.</t>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6124,19 +6139,8 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>Kalkrik väldränerad granskog intill Kultsjöån.</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6146,14 +6150,10 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Sara Forsström, Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr">
-        <is>
-          <t>Uppföljning bombmurkla 2025</t>
-        </is>
-      </c>
+          <t>Isak Vahlström, Sara Forsström</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43595-2023 artfynd.xlsx
+++ b/artfynd/A 43595-2023 artfynd.xlsx
@@ -5663,17 +5663,17 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Sara Forsström, Isak Vahlström</t>
+          <t>Isak Vahlström, Sara Forsström</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124495747</v>
+        <v>124496447</v>
       </c>
       <c r="B44" t="n">
-        <v>83424</v>
+        <v>100188</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5682,47 +5682,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1445</v>
+        <v>222771</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Staaloennjuana, Staaloennjuana, Ås lm</t>
+          <t>Stalonnäset, Stalonnäset, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540334</v>
+        <v>540359</v>
       </c>
       <c r="R44" t="n">
-        <v>7201784</v>
+        <v>7201824</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5754,7 +5745,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5764,7 +5755,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5791,10 +5782,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124496447</v>
+        <v>124495747</v>
       </c>
       <c r="B45" t="n">
-        <v>100188</v>
+        <v>83424</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5803,38 +5794,47 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222771</v>
+        <v>1445</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Stalonnäset, Stalonnäset, Ås lm</t>
+          <t>Staaloennjuana, Staaloennjuana, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>540359</v>
+        <v>540334</v>
       </c>
       <c r="R45" t="n">
-        <v>7201824</v>
+        <v>7201784</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5866,7 +5866,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5903,7 +5903,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124530286</v>
+        <v>124529574</v>
       </c>
       <c r="B46" t="n">
         <v>83424</v>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5946,8 +5946,6 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Stalons kalkgranskog, Ås lm</t>
@@ -5957,10 +5955,10 @@
         <v>540322</v>
       </c>
       <c r="R46" t="n">
-        <v>7201771</v>
+        <v>7201758</v>
       </c>
       <c r="S46" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5987,14 +5985,19 @@
           <t>2025-04-27</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-04-27</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ny lokal! Totalt hittades 4 fruktkroppar fördelade under tre olika granar. Statusen på växtplatsen bedöms som god men vinterns stormar har gjort att många kvistar blåst ner från granarna, vilket möjligen påverkar lokalen tillfälligt närmsta åren. Några träd har också blåst omkull i skogen men ingen större påverkan där bombmurklorna växer. Lokalen är oskyddad.</t>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6003,19 +6006,8 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>Kalkrik väldränerad granskog intill Kultsjöån.</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -6028,15 +6020,11 @@
           <t>Isak Vahlström, Sara Forsström</t>
         </is>
       </c>
-      <c r="AY46" t="inlineStr">
-        <is>
-          <t>Uppföljning bombmurkla 2025</t>
-        </is>
-      </c>
+      <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124529574</v>
+        <v>124530286</v>
       </c>
       <c r="B47" t="n">
         <v>83424</v>
@@ -6071,7 +6059,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6079,6 +6067,8 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Stalons kalkgranskog, Ås lm</t>
@@ -6088,10 +6078,10 @@
         <v>540322</v>
       </c>
       <c r="R47" t="n">
-        <v>7201758</v>
+        <v>7201771</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6118,19 +6108,14 @@
           <t>2025-04-27</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>13:46</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-04-27</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>13:46</t>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ny lokal! Totalt hittades 4 fruktkroppar fördelade under tre olika granar. Statusen på växtplatsen bedöms som god men vinterns stormar har gjort att många kvistar blåst ner från granarna, vilket möjligen påverkar lokalen tillfälligt närmsta åren. Några träd har också blåst omkull i skogen men ingen större påverkan där bombmurklorna växer. Lokalen är oskyddad.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6139,8 +6124,19 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>Kalkrik väldränerad granskog intill Kultsjöån.</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6150,10 +6146,14 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Sara Forsström</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
+          <t>Sara Forsström, Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Uppföljning bombmurkla 2025</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43595-2023 artfynd.xlsx
+++ b/artfynd/A 43595-2023 artfynd.xlsx
@@ -5558,7 +5558,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124495808</v>
+        <v>124495747</v>
       </c>
       <c r="B43" t="n">
         <v>83424</v>
@@ -5591,14 +5591,23 @@
           <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Staaloennjuana, Staaloennjuana, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540320</v>
+        <v>540334</v>
       </c>
       <c r="R43" t="n">
         <v>7201784</v>
@@ -5663,7 +5672,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Sara Forsström</t>
+          <t>Sara Forsström, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5782,7 +5791,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124495747</v>
+        <v>124495808</v>
       </c>
       <c r="B45" t="n">
         <v>83424</v>
@@ -5815,23 +5824,14 @@
           <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Staaloennjuana, Staaloennjuana, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>540334</v>
+        <v>540320</v>
       </c>
       <c r="R45" t="n">
         <v>7201784</v>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Sara Forsström, Isak Vahlström</t>
+          <t>Isak Vahlström, Sara Forsström</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">

--- a/artfynd/A 43595-2023 artfynd.xlsx
+++ b/artfynd/A 43595-2023 artfynd.xlsx
@@ -5558,10 +5558,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124495747</v>
+        <v>124496447</v>
       </c>
       <c r="B43" t="n">
-        <v>83424</v>
+        <v>100188</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5570,47 +5570,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1445</v>
+        <v>222771</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Staaloennjuana, Staaloennjuana, Ås lm</t>
+          <t>Stalonnäset, Stalonnäset, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540334</v>
+        <v>540359</v>
       </c>
       <c r="R43" t="n">
-        <v>7201784</v>
+        <v>7201824</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5642,7 +5633,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5652,7 +5643,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5679,10 +5670,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124496447</v>
+        <v>124495747</v>
       </c>
       <c r="B44" t="n">
-        <v>100188</v>
+        <v>83424</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5691,38 +5682,47 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222771</v>
+        <v>1445</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Stalonnäset, Stalonnäset, Ås lm</t>
+          <t>Staaloennjuana, Staaloennjuana, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540359</v>
+        <v>540334</v>
       </c>
       <c r="R44" t="n">
-        <v>7201824</v>
+        <v>7201784</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5754,7 +5754,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5764,7 +5764,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD44" t="b">

--- a/artfynd/A 43595-2023 artfynd.xlsx
+++ b/artfynd/A 43595-2023 artfynd.xlsx
@@ -5558,10 +5558,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124496447</v>
+        <v>124495747</v>
       </c>
       <c r="B43" t="n">
-        <v>100188</v>
+        <v>83424</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5570,38 +5570,47 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222771</v>
+        <v>1445</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Stalonnäset, Stalonnäset, Ås lm</t>
+          <t>Staaloennjuana, Staaloennjuana, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540359</v>
+        <v>540334</v>
       </c>
       <c r="R43" t="n">
-        <v>7201824</v>
+        <v>7201784</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5633,7 +5642,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5643,7 +5652,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5670,7 +5679,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124495747</v>
+        <v>124495808</v>
       </c>
       <c r="B44" t="n">
         <v>83424</v>
@@ -5703,23 +5712,14 @@
           <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Staaloennjuana, Staaloennjuana, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540334</v>
+        <v>540320</v>
       </c>
       <c r="R44" t="n">
         <v>7201784</v>
@@ -5791,10 +5791,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124495808</v>
+        <v>124496447</v>
       </c>
       <c r="B45" t="n">
-        <v>83424</v>
+        <v>100188</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5803,38 +5803,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1445</v>
+        <v>222771</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Staaloennjuana, Staaloennjuana, Ås lm</t>
+          <t>Stalonnäset, Stalonnäset, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>540320</v>
+        <v>540359</v>
       </c>
       <c r="R45" t="n">
-        <v>7201784</v>
+        <v>7201824</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5866,7 +5866,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5903,7 +5903,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124529574</v>
+        <v>124530286</v>
       </c>
       <c r="B46" t="n">
         <v>83424</v>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5946,6 +5946,8 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Stalons kalkgranskog, Ås lm</t>
@@ -5955,10 +5957,10 @@
         <v>540322</v>
       </c>
       <c r="R46" t="n">
-        <v>7201758</v>
+        <v>7201771</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5985,19 +5987,14 @@
           <t>2025-04-27</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>13:46</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-04-27</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>13:46</t>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ny lokal! Totalt hittades 4 fruktkroppar fördelade under tre olika granar. Statusen på växtplatsen bedöms som god men vinterns stormar har gjort att många kvistar blåst ner från granarna, vilket möjligen påverkar lokalen tillfälligt närmsta åren. Några träd har också blåst omkull i skogen men ingen större påverkan där bombmurklorna växer. Lokalen är oskyddad.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6006,8 +6003,19 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>Kalkrik väldränerad granskog intill Kultsjöån.</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -6017,14 +6025,18 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Sara Forsström</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr"/>
+          <t>Sara Forsström, Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Uppföljning bombmurkla 2025</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124530286</v>
+        <v>124529574</v>
       </c>
       <c r="B47" t="n">
         <v>83424</v>
@@ -6059,7 +6071,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6067,8 +6079,6 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Stalons kalkgranskog, Ås lm</t>
@@ -6078,10 +6088,10 @@
         <v>540322</v>
       </c>
       <c r="R47" t="n">
-        <v>7201771</v>
+        <v>7201758</v>
       </c>
       <c r="S47" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6108,14 +6118,19 @@
           <t>2025-04-27</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-04-27</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ny lokal! Totalt hittades 4 fruktkroppar fördelade under tre olika granar. Statusen på växtplatsen bedöms som god men vinterns stormar har gjort att många kvistar blåst ner från granarna, vilket möjligen påverkar lokalen tillfälligt närmsta åren. Några träd har också blåst omkull i skogen men ingen större påverkan där bombmurklorna växer. Lokalen är oskyddad.</t>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6124,19 +6139,8 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>Kalkrik väldränerad granskog intill Kultsjöån.</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6149,11 +6153,7 @@
           <t>Isak Vahlström, Sara Forsström</t>
         </is>
       </c>
-      <c r="AY47" t="inlineStr">
-        <is>
-          <t>Uppföljning bombmurkla 2025</t>
-        </is>
-      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43595-2023 artfynd.xlsx
+++ b/artfynd/A 43595-2023 artfynd.xlsx
@@ -5679,10 +5679,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124495808</v>
+        <v>124496447</v>
       </c>
       <c r="B44" t="n">
-        <v>83424</v>
+        <v>100188</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5691,38 +5691,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1445</v>
+        <v>222771</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Staaloennjuana, Staaloennjuana, Ås lm</t>
+          <t>Stalonnäset, Stalonnäset, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540320</v>
+        <v>540359</v>
       </c>
       <c r="R44" t="n">
-        <v>7201784</v>
+        <v>7201824</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5754,7 +5754,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5764,7 +5764,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5791,10 +5791,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124496447</v>
+        <v>124495808</v>
       </c>
       <c r="B45" t="n">
-        <v>100188</v>
+        <v>83424</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5803,38 +5803,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222771</v>
+        <v>1445</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Stalonnäset, Stalonnäset, Ås lm</t>
+          <t>Staaloennjuana, Staaloennjuana, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>540359</v>
+        <v>540320</v>
       </c>
       <c r="R45" t="n">
-        <v>7201824</v>
+        <v>7201784</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5866,7 +5866,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 43595-2023 artfynd.xlsx
+++ b/artfynd/A 43595-2023 artfynd.xlsx
@@ -5903,7 +5903,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124530286</v>
+        <v>124529574</v>
       </c>
       <c r="B46" t="n">
         <v>83424</v>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5946,8 +5946,6 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Stalons kalkgranskog, Ås lm</t>
@@ -5957,10 +5955,10 @@
         <v>540322</v>
       </c>
       <c r="R46" t="n">
-        <v>7201771</v>
+        <v>7201758</v>
       </c>
       <c r="S46" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5987,14 +5985,19 @@
           <t>2025-04-27</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-04-27</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ny lokal! Totalt hittades 4 fruktkroppar fördelade under tre olika granar. Statusen på växtplatsen bedöms som god men vinterns stormar har gjort att många kvistar blåst ner från granarna, vilket möjligen påverkar lokalen tillfälligt närmsta åren. Några träd har också blåst omkull i skogen men ingen större påverkan där bombmurklorna växer. Lokalen är oskyddad.</t>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6003,19 +6006,8 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>Kalkrik väldränerad granskog intill Kultsjöån.</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -6025,18 +6017,14 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Sara Forsström, Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr">
-        <is>
-          <t>Uppföljning bombmurkla 2025</t>
-        </is>
-      </c>
+          <t>Isak Vahlström, Sara Forsström</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124529574</v>
+        <v>124530286</v>
       </c>
       <c r="B47" t="n">
         <v>83424</v>
@@ -6071,7 +6059,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6079,6 +6067,8 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Stalons kalkgranskog, Ås lm</t>
@@ -6088,10 +6078,10 @@
         <v>540322</v>
       </c>
       <c r="R47" t="n">
-        <v>7201758</v>
+        <v>7201771</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6118,19 +6108,14 @@
           <t>2025-04-27</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>13:46</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-04-27</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>13:46</t>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ny lokal! Totalt hittades 4 fruktkroppar fördelade under tre olika granar. Statusen på växtplatsen bedöms som god men vinterns stormar har gjort att många kvistar blåst ner från granarna, vilket möjligen påverkar lokalen tillfälligt närmsta åren. Några träd har också blåst omkull i skogen men ingen större påverkan där bombmurklorna växer. Lokalen är oskyddad.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6139,8 +6124,19 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>Kalkrik väldränerad granskog intill Kultsjöån.</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6153,7 +6149,11 @@
           <t>Isak Vahlström, Sara Forsström</t>
         </is>
       </c>
-      <c r="AY47" t="inlineStr"/>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Uppföljning bombmurkla 2025</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43595-2023 artfynd.xlsx
+++ b/artfynd/A 43595-2023 artfynd.xlsx
@@ -5558,7 +5558,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124495747</v>
+        <v>124495808</v>
       </c>
       <c r="B43" t="n">
         <v>83424</v>
@@ -5591,23 +5591,14 @@
           <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Staaloennjuana, Staaloennjuana, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540334</v>
+        <v>540320</v>
       </c>
       <c r="R43" t="n">
         <v>7201784</v>
@@ -5791,7 +5782,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124495808</v>
+        <v>124495747</v>
       </c>
       <c r="B45" t="n">
         <v>83424</v>
@@ -5824,14 +5815,23 @@
           <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Staaloennjuana, Staaloennjuana, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>540320</v>
+        <v>540334</v>
       </c>
       <c r="R45" t="n">
         <v>7201784</v>
@@ -5903,7 +5903,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124529574</v>
+        <v>124530286</v>
       </c>
       <c r="B46" t="n">
         <v>83424</v>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5946,6 +5946,8 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Stalons kalkgranskog, Ås lm</t>
@@ -5955,10 +5957,10 @@
         <v>540322</v>
       </c>
       <c r="R46" t="n">
-        <v>7201758</v>
+        <v>7201771</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5985,19 +5987,14 @@
           <t>2025-04-27</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>13:46</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-04-27</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>13:46</t>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ny lokal! Totalt hittades 4 fruktkroppar fördelade under tre olika granar. Statusen på växtplatsen bedöms som god men vinterns stormar har gjort att många kvistar blåst ner från granarna, vilket möjligen påverkar lokalen tillfälligt närmsta åren. Några träd har också blåst omkull i skogen men ingen större påverkan där bombmurklorna växer. Lokalen är oskyddad.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6006,8 +6003,19 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>Kalkrik väldränerad granskog intill Kultsjöån.</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -6020,11 +6028,15 @@
           <t>Isak Vahlström, Sara Forsström</t>
         </is>
       </c>
-      <c r="AY46" t="inlineStr"/>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Uppföljning bombmurkla 2025</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124530286</v>
+        <v>124529574</v>
       </c>
       <c r="B47" t="n">
         <v>83424</v>
@@ -6059,7 +6071,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6067,8 +6079,6 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Stalons kalkgranskog, Ås lm</t>
@@ -6078,10 +6088,10 @@
         <v>540322</v>
       </c>
       <c r="R47" t="n">
-        <v>7201771</v>
+        <v>7201758</v>
       </c>
       <c r="S47" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6108,14 +6118,19 @@
           <t>2025-04-27</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-04-27</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ny lokal! Totalt hittades 4 fruktkroppar fördelade under tre olika granar. Statusen på växtplatsen bedöms som god men vinterns stormar har gjort att många kvistar blåst ner från granarna, vilket möjligen påverkar lokalen tillfälligt närmsta åren. Några träd har också blåst omkull i skogen men ingen större påverkan där bombmurklorna växer. Lokalen är oskyddad.</t>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6124,19 +6139,8 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>Kalkrik väldränerad granskog intill Kultsjöån.</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6149,11 +6153,7 @@
           <t>Isak Vahlström, Sara Forsström</t>
         </is>
       </c>
-      <c r="AY47" t="inlineStr">
-        <is>
-          <t>Uppföljning bombmurkla 2025</t>
-        </is>
-      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43595-2023 artfynd.xlsx
+++ b/artfynd/A 43595-2023 artfynd.xlsx
@@ -5558,10 +5558,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124495808</v>
+        <v>124496447</v>
       </c>
       <c r="B43" t="n">
-        <v>83424</v>
+        <v>100188</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5570,38 +5570,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1445</v>
+        <v>222771</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Staaloennjuana, Staaloennjuana, Ås lm</t>
+          <t>Stalonnäset, Stalonnäset, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540320</v>
+        <v>540359</v>
       </c>
       <c r="R43" t="n">
-        <v>7201784</v>
+        <v>7201824</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5633,7 +5633,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5670,10 +5670,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124496447</v>
+        <v>124495808</v>
       </c>
       <c r="B44" t="n">
-        <v>100188</v>
+        <v>83424</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5682,38 +5682,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222771</v>
+        <v>1445</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Stalonnäset, Stalonnäset, Ås lm</t>
+          <t>Staaloennjuana, Staaloennjuana, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540359</v>
+        <v>540320</v>
       </c>
       <c r="R44" t="n">
-        <v>7201824</v>
+        <v>7201784</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5745,7 +5745,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5755,7 +5755,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Sara Forsström, Isak Vahlström</t>
+          <t>Isak Vahlström, Sara Forsström</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>

--- a/artfynd/A 43595-2023 artfynd.xlsx
+++ b/artfynd/A 43595-2023 artfynd.xlsx
@@ -5558,10 +5558,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124496447</v>
+        <v>124495808</v>
       </c>
       <c r="B43" t="n">
-        <v>100188</v>
+        <v>83424</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5570,38 +5570,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222771</v>
+        <v>1445</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Stalonnäset, Stalonnäset, Ås lm</t>
+          <t>Staaloennjuana, Staaloennjuana, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540359</v>
+        <v>540320</v>
       </c>
       <c r="R43" t="n">
-        <v>7201824</v>
+        <v>7201784</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5633,7 +5633,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5670,10 +5670,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124495808</v>
+        <v>124496447</v>
       </c>
       <c r="B44" t="n">
-        <v>83424</v>
+        <v>100188</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5682,38 +5682,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1445</v>
+        <v>222771</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Staaloennjuana, Staaloennjuana, Ås lm</t>
+          <t>Stalonnäset, Stalonnäset, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540320</v>
+        <v>540359</v>
       </c>
       <c r="R44" t="n">
-        <v>7201784</v>
+        <v>7201824</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5745,7 +5745,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5755,7 +5755,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5903,7 +5903,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124530286</v>
+        <v>124529574</v>
       </c>
       <c r="B46" t="n">
         <v>83424</v>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5946,8 +5946,6 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Stalons kalkgranskog, Ås lm</t>
@@ -5957,10 +5955,10 @@
         <v>540322</v>
       </c>
       <c r="R46" t="n">
-        <v>7201771</v>
+        <v>7201758</v>
       </c>
       <c r="S46" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5987,14 +5985,19 @@
           <t>2025-04-27</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-04-27</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ny lokal! Totalt hittades 4 fruktkroppar fördelade under tre olika granar. Statusen på växtplatsen bedöms som god men vinterns stormar har gjort att många kvistar blåst ner från granarna, vilket möjligen påverkar lokalen tillfälligt närmsta åren. Några träd har också blåst omkull i skogen men ingen större påverkan där bombmurklorna växer. Lokalen är oskyddad.</t>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6003,19 +6006,8 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>Kalkrik väldränerad granskog intill Kultsjöån.</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -6028,15 +6020,11 @@
           <t>Isak Vahlström, Sara Forsström</t>
         </is>
       </c>
-      <c r="AY46" t="inlineStr">
-        <is>
-          <t>Uppföljning bombmurkla 2025</t>
-        </is>
-      </c>
+      <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124529574</v>
+        <v>124530286</v>
       </c>
       <c r="B47" t="n">
         <v>83424</v>
@@ -6071,7 +6059,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6079,6 +6067,8 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Stalons kalkgranskog, Ås lm</t>
@@ -6088,10 +6078,10 @@
         <v>540322</v>
       </c>
       <c r="R47" t="n">
-        <v>7201758</v>
+        <v>7201771</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6118,19 +6108,14 @@
           <t>2025-04-27</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>13:46</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-04-27</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>13:46</t>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ny lokal! Totalt hittades 4 fruktkroppar fördelade under tre olika granar. Statusen på växtplatsen bedöms som god men vinterns stormar har gjort att många kvistar blåst ner från granarna, vilket möjligen påverkar lokalen tillfälligt närmsta åren. Några träd har också blåst omkull i skogen men ingen större påverkan där bombmurklorna växer. Lokalen är oskyddad.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6139,8 +6124,19 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>Kalkrik väldränerad granskog intill Kultsjöån.</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6153,7 +6149,11 @@
           <t>Isak Vahlström, Sara Forsström</t>
         </is>
       </c>
-      <c r="AY47" t="inlineStr"/>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Uppföljning bombmurkla 2025</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43595-2023 artfynd.xlsx
+++ b/artfynd/A 43595-2023 artfynd.xlsx
@@ -5558,7 +5558,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124495808</v>
+        <v>124495747</v>
       </c>
       <c r="B43" t="n">
         <v>83424</v>
@@ -5591,14 +5591,23 @@
           <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Staaloennjuana, Staaloennjuana, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540320</v>
+        <v>540334</v>
       </c>
       <c r="R43" t="n">
         <v>7201784</v>
@@ -5775,14 +5784,14 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Sara Forsström</t>
+          <t>Sara Forsström, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124495747</v>
+        <v>124495808</v>
       </c>
       <c r="B45" t="n">
         <v>83424</v>
@@ -5815,23 +5824,14 @@
           <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Staaloennjuana, Staaloennjuana, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>540334</v>
+        <v>540320</v>
       </c>
       <c r="R45" t="n">
         <v>7201784</v>
@@ -5896,7 +5896,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Sara Forsström, Isak Vahlström</t>
+          <t>Isak Vahlström, Sara Forsström</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>

--- a/artfynd/A 43595-2023 artfynd.xlsx
+++ b/artfynd/A 43595-2023 artfynd.xlsx
@@ -5558,10 +5558,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124495747</v>
+        <v>124496447</v>
       </c>
       <c r="B43" t="n">
-        <v>83424</v>
+        <v>100188</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5570,47 +5570,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1445</v>
+        <v>222771</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Staaloennjuana, Staaloennjuana, Ås lm</t>
+          <t>Stalonnäset, Stalonnäset, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540334</v>
+        <v>540359</v>
       </c>
       <c r="R43" t="n">
-        <v>7201784</v>
+        <v>7201824</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5642,7 +5633,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5652,7 +5643,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5679,10 +5670,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124496447</v>
+        <v>124495808</v>
       </c>
       <c r="B44" t="n">
-        <v>100188</v>
+        <v>83424</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5691,38 +5682,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222771</v>
+        <v>1445</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Stalonnäset, Stalonnäset, Ås lm</t>
+          <t>Staaloennjuana, Staaloennjuana, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540359</v>
+        <v>540320</v>
       </c>
       <c r="R44" t="n">
-        <v>7201824</v>
+        <v>7201784</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5754,7 +5745,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5764,7 +5755,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5791,7 +5782,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124495808</v>
+        <v>124495747</v>
       </c>
       <c r="B45" t="n">
         <v>83424</v>
@@ -5824,14 +5815,23 @@
           <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Staaloennjuana, Staaloennjuana, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>540320</v>
+        <v>540334</v>
       </c>
       <c r="R45" t="n">
         <v>7201784</v>
@@ -5896,7 +5896,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Sara Forsström</t>
+          <t>Sara Forsström, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>

--- a/artfynd/A 43595-2023 artfynd.xlsx
+++ b/artfynd/A 43595-2023 artfynd.xlsx
@@ -5558,10 +5558,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124496447</v>
+        <v>124495808</v>
       </c>
       <c r="B43" t="n">
-        <v>100188</v>
+        <v>83424</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5570,38 +5570,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222771</v>
+        <v>1445</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Stalonnäset, Stalonnäset, Ås lm</t>
+          <t>Staaloennjuana, Staaloennjuana, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540359</v>
+        <v>540320</v>
       </c>
       <c r="R43" t="n">
-        <v>7201824</v>
+        <v>7201784</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5633,7 +5633,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5670,10 +5670,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124495808</v>
+        <v>124496447</v>
       </c>
       <c r="B44" t="n">
-        <v>83424</v>
+        <v>100188</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5682,38 +5682,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1445</v>
+        <v>222771</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Staaloennjuana, Staaloennjuana, Ås lm</t>
+          <t>Stalonnäset, Stalonnäset, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540320</v>
+        <v>540359</v>
       </c>
       <c r="R44" t="n">
-        <v>7201784</v>
+        <v>7201824</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5745,7 +5745,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5755,7 +5755,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5903,7 +5903,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124529574</v>
+        <v>124530286</v>
       </c>
       <c r="B46" t="n">
         <v>83424</v>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5946,6 +5946,8 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Stalons kalkgranskog, Ås lm</t>
@@ -5955,10 +5957,10 @@
         <v>540322</v>
       </c>
       <c r="R46" t="n">
-        <v>7201758</v>
+        <v>7201771</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5985,19 +5987,14 @@
           <t>2025-04-27</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>13:46</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-04-27</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>13:46</t>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ny lokal! Totalt hittades 4 fruktkroppar fördelade under tre olika granar. Statusen på växtplatsen bedöms som god men vinterns stormar har gjort att många kvistar blåst ner från granarna, vilket möjligen påverkar lokalen tillfälligt närmsta åren. Några träd har också blåst omkull i skogen men ingen större påverkan där bombmurklorna växer. Lokalen är oskyddad.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6006,8 +6003,19 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>Kalkrik väldränerad granskog intill Kultsjöån.</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -6020,11 +6028,15 @@
           <t>Isak Vahlström, Sara Forsström</t>
         </is>
       </c>
-      <c r="AY46" t="inlineStr"/>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Uppföljning bombmurkla 2025</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124530286</v>
+        <v>124529574</v>
       </c>
       <c r="B47" t="n">
         <v>83424</v>
@@ -6059,7 +6071,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6067,8 +6079,6 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Stalons kalkgranskog, Ås lm</t>
@@ -6078,10 +6088,10 @@
         <v>540322</v>
       </c>
       <c r="R47" t="n">
-        <v>7201771</v>
+        <v>7201758</v>
       </c>
       <c r="S47" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6108,14 +6118,19 @@
           <t>2025-04-27</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-04-27</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ny lokal! Totalt hittades 4 fruktkroppar fördelade under tre olika granar. Statusen på växtplatsen bedöms som god men vinterns stormar har gjort att många kvistar blåst ner från granarna, vilket möjligen påverkar lokalen tillfälligt närmsta åren. Några träd har också blåst omkull i skogen men ingen större påverkan där bombmurklorna växer. Lokalen är oskyddad.</t>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6124,19 +6139,8 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>Kalkrik väldränerad granskog intill Kultsjöån.</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6149,11 +6153,7 @@
           <t>Isak Vahlström, Sara Forsström</t>
         </is>
       </c>
-      <c r="AY47" t="inlineStr">
-        <is>
-          <t>Uppföljning bombmurkla 2025</t>
-        </is>
-      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43595-2023 artfynd.xlsx
+++ b/artfynd/A 43595-2023 artfynd.xlsx
@@ -5558,7 +5558,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124495808</v>
+        <v>124495747</v>
       </c>
       <c r="B43" t="n">
         <v>83424</v>
@@ -5591,14 +5591,23 @@
           <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Staaloennjuana, Staaloennjuana, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540320</v>
+        <v>540334</v>
       </c>
       <c r="R43" t="n">
         <v>7201784</v>
@@ -5670,10 +5679,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124496447</v>
+        <v>124495808</v>
       </c>
       <c r="B44" t="n">
-        <v>100188</v>
+        <v>83424</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5682,38 +5691,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222771</v>
+        <v>1445</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Stalonnäset, Stalonnäset, Ås lm</t>
+          <t>Staaloennjuana, Staaloennjuana, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540359</v>
+        <v>540320</v>
       </c>
       <c r="R44" t="n">
-        <v>7201824</v>
+        <v>7201784</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5745,7 +5754,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5755,7 +5764,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5782,10 +5791,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124495747</v>
+        <v>124496447</v>
       </c>
       <c r="B45" t="n">
-        <v>83424</v>
+        <v>100188</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5794,47 +5803,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1445</v>
+        <v>222771</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Staaloennjuana, Staaloennjuana, Ås lm</t>
+          <t>Stalonnäset, Stalonnäset, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>540334</v>
+        <v>540359</v>
       </c>
       <c r="R45" t="n">
-        <v>7201784</v>
+        <v>7201824</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5866,7 +5866,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 43595-2023 artfynd.xlsx
+++ b/artfynd/A 43595-2023 artfynd.xlsx
@@ -5558,7 +5558,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124495747</v>
+        <v>124495808</v>
       </c>
       <c r="B43" t="n">
         <v>83424</v>
@@ -5591,23 +5591,14 @@
           <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Staaloennjuana, Staaloennjuana, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540334</v>
+        <v>540320</v>
       </c>
       <c r="R43" t="n">
         <v>7201784</v>
@@ -5679,7 +5670,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124495808</v>
+        <v>124495747</v>
       </c>
       <c r="B44" t="n">
         <v>83424</v>
@@ -5712,14 +5703,23 @@
           <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Staaloennjuana, Staaloennjuana, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540320</v>
+        <v>540334</v>
       </c>
       <c r="R44" t="n">
         <v>7201784</v>
@@ -5903,7 +5903,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124530286</v>
+        <v>124529574</v>
       </c>
       <c r="B46" t="n">
         <v>83424</v>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5946,8 +5946,6 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Stalons kalkgranskog, Ås lm</t>
@@ -5957,10 +5955,10 @@
         <v>540322</v>
       </c>
       <c r="R46" t="n">
-        <v>7201771</v>
+        <v>7201758</v>
       </c>
       <c r="S46" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5987,14 +5985,19 @@
           <t>2025-04-27</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-04-27</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ny lokal! Totalt hittades 4 fruktkroppar fördelade under tre olika granar. Statusen på växtplatsen bedöms som god men vinterns stormar har gjort att många kvistar blåst ner från granarna, vilket möjligen påverkar lokalen tillfälligt närmsta åren. Några träd har också blåst omkull i skogen men ingen större påverkan där bombmurklorna växer. Lokalen är oskyddad.</t>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6003,19 +6006,8 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>Kalkrik väldränerad granskog intill Kultsjöån.</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -6028,15 +6020,11 @@
           <t>Isak Vahlström, Sara Forsström</t>
         </is>
       </c>
-      <c r="AY46" t="inlineStr">
-        <is>
-          <t>Uppföljning bombmurkla 2025</t>
-        </is>
-      </c>
+      <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124529574</v>
+        <v>124530286</v>
       </c>
       <c r="B47" t="n">
         <v>83424</v>
@@ -6071,7 +6059,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6079,6 +6067,8 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Stalons kalkgranskog, Ås lm</t>
@@ -6088,10 +6078,10 @@
         <v>540322</v>
       </c>
       <c r="R47" t="n">
-        <v>7201758</v>
+        <v>7201771</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6118,19 +6108,14 @@
           <t>2025-04-27</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>13:46</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-04-27</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>13:46</t>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ny lokal! Totalt hittades 4 fruktkroppar fördelade under tre olika granar. Statusen på växtplatsen bedöms som god men vinterns stormar har gjort att många kvistar blåst ner från granarna, vilket möjligen påverkar lokalen tillfälligt närmsta åren. Några träd har också blåst omkull i skogen men ingen större påverkan där bombmurklorna växer. Lokalen är oskyddad.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6139,8 +6124,19 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>Kalkrik väldränerad granskog intill Kultsjöån.</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6153,7 +6149,11 @@
           <t>Isak Vahlström, Sara Forsström</t>
         </is>
       </c>
-      <c r="AY47" t="inlineStr"/>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Uppföljning bombmurkla 2025</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43595-2023 artfynd.xlsx
+++ b/artfynd/A 43595-2023 artfynd.xlsx
@@ -5558,7 +5558,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124495808</v>
+        <v>124495747</v>
       </c>
       <c r="B43" t="n">
         <v>83424</v>
@@ -5591,14 +5591,23 @@
           <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Staaloennjuana, Staaloennjuana, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540320</v>
+        <v>540334</v>
       </c>
       <c r="R43" t="n">
         <v>7201784</v>
@@ -5670,7 +5679,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124495747</v>
+        <v>124495808</v>
       </c>
       <c r="B44" t="n">
         <v>83424</v>
@@ -5703,23 +5712,14 @@
           <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Staaloennjuana, Staaloennjuana, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540334</v>
+        <v>540320</v>
       </c>
       <c r="R44" t="n">
         <v>7201784</v>
@@ -5784,7 +5784,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Sara Forsström, Isak Vahlström</t>
+          <t>Isak Vahlström, Sara Forsström</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5903,7 +5903,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124529574</v>
+        <v>124530286</v>
       </c>
       <c r="B46" t="n">
         <v>83424</v>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5946,6 +5946,8 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Stalons kalkgranskog, Ås lm</t>
@@ -5955,10 +5957,10 @@
         <v>540322</v>
       </c>
       <c r="R46" t="n">
-        <v>7201758</v>
+        <v>7201771</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5985,19 +5987,14 @@
           <t>2025-04-27</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>13:46</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-04-27</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>13:46</t>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ny lokal! Totalt hittades 4 fruktkroppar fördelade under tre olika granar. Statusen på växtplatsen bedöms som god men vinterns stormar har gjort att många kvistar blåst ner från granarna, vilket möjligen påverkar lokalen tillfälligt närmsta åren. Några träd har också blåst omkull i skogen men ingen större påverkan där bombmurklorna växer. Lokalen är oskyddad.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6006,8 +6003,19 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>Kalkrik väldränerad granskog intill Kultsjöån.</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -6020,11 +6028,15 @@
           <t>Isak Vahlström, Sara Forsström</t>
         </is>
       </c>
-      <c r="AY46" t="inlineStr"/>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Uppföljning bombmurkla 2025</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124530286</v>
+        <v>124529574</v>
       </c>
       <c r="B47" t="n">
         <v>83424</v>
@@ -6059,7 +6071,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6067,8 +6079,6 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Stalons kalkgranskog, Ås lm</t>
@@ -6078,10 +6088,10 @@
         <v>540322</v>
       </c>
       <c r="R47" t="n">
-        <v>7201771</v>
+        <v>7201758</v>
       </c>
       <c r="S47" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6108,14 +6118,19 @@
           <t>2025-04-27</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-04-27</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ny lokal! Totalt hittades 4 fruktkroppar fördelade under tre olika granar. Statusen på växtplatsen bedöms som god men vinterns stormar har gjort att många kvistar blåst ner från granarna, vilket möjligen påverkar lokalen tillfälligt närmsta åren. Några träd har också blåst omkull i skogen men ingen större påverkan där bombmurklorna växer. Lokalen är oskyddad.</t>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6124,19 +6139,8 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>Kalkrik väldränerad granskog intill Kultsjöån.</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6149,11 +6153,7 @@
           <t>Isak Vahlström, Sara Forsström</t>
         </is>
       </c>
-      <c r="AY47" t="inlineStr">
-        <is>
-          <t>Uppföljning bombmurkla 2025</t>
-        </is>
-      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
